--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,40 +1994,40 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,40 +2258,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,40 +2258,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2186,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>2.32</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>8.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.63</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL32"/>
+  <dimension ref="A1:AO32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,115 +513,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>Odd_A_HT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_H_HT1</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_D_HT1</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_A_HT1</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>awayGoals</t>
+          <t>Odd_DNB_H</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_DNB_A</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -727,11 +742,15 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -745,17 +764,22 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
       </c>
     </row>
@@ -859,11 +883,15 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -877,17 +905,22 @@
       <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
       </c>
     </row>
@@ -991,11 +1024,15 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1009,17 +1046,22 @@
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="3" t="n">
         <v>45889.45833333334</v>
       </c>
     </row>
@@ -1123,11 +1165,15 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1141,17 +1187,22 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="3" t="n">
         <v>45889.5</v>
       </c>
     </row>
@@ -1255,11 +1306,15 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1273,17 +1328,22 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="3" t="n">
         <v>45889.5</v>
       </c>
     </row>
@@ -1387,11 +1447,15 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1405,17 +1469,22 @@
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3" t="n">
         <v>45889.5</v>
       </c>
     </row>
@@ -1519,11 +1588,15 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1537,17 +1610,22 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3" t="n">
         <v>45889.5</v>
       </c>
     </row>
@@ -1651,11 +1729,15 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1669,17 +1751,22 @@
       <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="3" t="n">
         <v>45889.5</v>
       </c>
     </row>
@@ -1783,11 +1870,15 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1801,17 +1892,22 @@
       <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -1874,76 +1970,85 @@
         <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AN11" t="n">
         <v>1.4</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -2006,76 +2111,85 @@
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN12" t="n">
         <v>3.7</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -2138,34 +2252,34 @@
         <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2177,37 +2291,46 @@
         <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.67</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -2311,11 +2434,15 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2329,17 +2456,22 @@
       <c r="AI14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -2443,11 +2575,15 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2461,17 +2597,22 @@
       <c r="AI15" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -2575,11 +2716,15 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2593,17 +2738,22 @@
       <c r="AI16" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
       </c>
     </row>
@@ -2707,11 +2857,15 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2725,17 +2879,22 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
       </c>
     </row>
@@ -2839,11 +2998,15 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2857,17 +3020,22 @@
       <c r="AI18" t="n">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
       </c>
     </row>
@@ -2954,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -2966,16 +3134,20 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2989,17 +3161,22 @@
       <c r="AI19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="3" t="n">
         <v>45889.60416666666</v>
       </c>
     </row>
@@ -3103,11 +3280,15 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3121,17 +3302,22 @@
       <c r="AI20" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3" t="n">
         <v>45889.625</v>
       </c>
     </row>
@@ -3235,11 +3421,15 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3253,17 +3443,22 @@
       <c r="AI21" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="3" t="n">
         <v>45889.625</v>
       </c>
     </row>
@@ -3367,11 +3562,15 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3385,17 +3584,22 @@
       <c r="AI22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3" t="n">
         <v>45889.64583333334</v>
       </c>
     </row>
@@ -3499,11 +3703,15 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3517,17 +3725,22 @@
       <c r="AI23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="3" t="n">
         <v>45889.65625</v>
       </c>
     </row>
@@ -3631,11 +3844,15 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3649,17 +3866,22 @@
       <c r="AI24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
       </c>
     </row>
@@ -3746,28 +3968,32 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3781,17 +4007,22 @@
       <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
       </c>
     </row>
@@ -3878,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3890,16 +4121,20 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3913,17 +4148,22 @@
       <c r="AI26" t="n">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL26" s="3" t="n">
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3" t="n">
         <v>45889.79166666666</v>
       </c>
     </row>
@@ -4027,11 +4267,15 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4045,17 +4289,22 @@
       <c r="AI27" t="n">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL27" s="3" t="n">
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3" t="n">
         <v>45889.79166666666</v>
       </c>
     </row>
@@ -4159,11 +4408,15 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4177,17 +4430,22 @@
       <c r="AI28" t="n">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL28" s="3" t="n">
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3" t="n">
         <v>45889.83333333334</v>
       </c>
     </row>
@@ -4250,76 +4508,85 @@
         <v>1.57</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.5</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN29" t="n">
         <v>2.5</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL29" s="3" t="n">
+      <c r="AO29" s="3" t="n">
         <v>45889.85416666666</v>
       </c>
     </row>
@@ -4423,11 +4690,15 @@
       <c r="AC30" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4441,17 +4712,22 @@
       <c r="AI30" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="n">
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3" t="n">
         <v>45889.875</v>
       </c>
     </row>
@@ -4555,11 +4831,15 @@
       <c r="AC31" t="n">
         <v>0</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4573,17 +4853,22 @@
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL31" s="3" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
         <v>45889.89583333334</v>
       </c>
     </row>
@@ -4687,11 +4972,15 @@
       <c r="AC32" t="n">
         <v>0</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4705,17 +4994,22 @@
       <c r="AI32" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.81</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>1.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="R12" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
         <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>5.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,55 +2240,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.5</v>
       </c>
-      <c r="P13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X13" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>1.67</v>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.32</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.31</v>
+        <v>3.63</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>8.5</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>4.31</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AO33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1776,27 +1776,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="11">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,83 +2099,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>3.81</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
         <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH12" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>3.81</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.63</v>
+        <v>1.37</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.31</v>
+        <v>3.63</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="25">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4032,27 +4032,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,31 +4496,31 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4544,10 +4544,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4566,13 +4566,13 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,13 +4581,13 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4707,13 +4707,13 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.875</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="31">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.875</v>
       </c>
     </row>
     <row r="32">
@@ -4878,138 +4878,279 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
+        <v>45889.89583333334</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Orange County SC</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>45889.45833333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="6">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1776,27 +1776,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2763,27 +2763,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.81</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2948,10 +2948,10 @@
         <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="21">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4032,27 +4032,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="27">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="28">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,31 +4355,31 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.65</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="29">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.875</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4707,13 +4707,13 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="31">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4869,288 +4869,6 @@
         <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="3" t="n">
-        <v>45889.89583333334</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO31"/>
+  <dimension ref="A1:AO30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.52083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.71</v>
       </c>
       <c r="M10" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.25</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,55 +1958,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>1.67</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2622,27 +2622,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3686,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3750,27 +3750,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3821,22 +3821,22 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3891,27 +3891,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,13 +4017,13 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="26">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,31 +4214,31 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4284,13 +4284,13 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="28">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,31 +4355,31 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.875</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.875</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4728,147 +4728,6 @@
         <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.89583333334</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,95 +1817,95 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.25</v>
       </c>
-      <c r="N10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
         <v>3.25</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AN10" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO30"/>
+  <dimension ref="A1:AO33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.5</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3686,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3750,27 +3750,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3821,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3891,27 +3891,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,13 +4017,13 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -4032,27 +4032,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,46 +4214,46 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W27" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4284,13 +4284,13 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45889.875</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,138 +4596,561 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Wilstermann</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>45889.85416666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
+        <v>45889.875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
+        <v>45889.89583333334</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Orange County SC</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>1.71</v>
       </c>
       <c r="M10" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.25</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,95 +2099,95 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O12" t="n">
         <v>3.25</v>
       </c>
-      <c r="N12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R12" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="S12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>3.25</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>12.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3686,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V27" t="n">
         <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>1.55</v>
       </c>
       <c r="W28" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,31 +1817,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1865,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1887,13 +1887,13 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>12.2</v>
+        <v>5.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z22" t="n">
         <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3689,10 +3689,10 @@
         <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
         <v>1.6</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V28" t="n">
         <v>1.55</v>
       </c>
       <c r="W28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,55 +1958,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>1.67</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>1.34</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>12.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3689,10 +3689,10 @@
         <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
         <v>1.6</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V27" t="n">
         <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>1.55</v>
       </c>
       <c r="W28" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,55 +2099,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>1.67</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V28" t="n">
         <v>1.55</v>
       </c>
       <c r="W28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,58 +1535,58 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,55 +2099,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.33</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>1.67</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.5</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.34</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>1.34</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="M17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3689,10 +3689,10 @@
         <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
         <v>1.6</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3971,10 +3971,10 @@
         <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>1.6</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V27" t="n">
         <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>1.55</v>
       </c>
       <c r="W28" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,55 +1535,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.33</v>
       </c>
-      <c r="P8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
         <v>1.67</v>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3686,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3971,10 +3971,10 @@
         <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
         <v>1.6</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>12.2</v>
+        <v>5.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z26" t="n">
         <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>1.34</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.84</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>1.34</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3686,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,95 +2381,95 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O14" t="n">
         <v>3.25</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
         <v>3.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AN14" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.875</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.95833333334</v>
       </c>
     </row>
     <row r="33">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>45889.52083333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="8">
@@ -1494,27 +1494,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,13 +1620,13 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="9">
@@ -1635,27 +1635,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>5.1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.75</v>
+        <v>3.81</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>1.52</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,13 +2607,13 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2622,27 +2622,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>1.84</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.34</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="21">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="24">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z24" t="n">
         <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,14 +4073,14 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
         <v>3.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4173,27 +4173,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4385,22 +4385,22 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,13 +4581,13 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,46 +4637,46 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>3.19</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W30" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4707,13 +4707,13 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,31 +4919,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.95833333334</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="33">
@@ -5019,138 +5019,420 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>45889.89583333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Colorado Rapids II</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Portland Timbers II</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="3" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3" t="n">
+        <v>45889.95833333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8.5</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.34</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.21</v>
+        <v>9.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>1.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.25</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="Z24" t="n">
         <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
         <v>1.6</v>
@@ -4673,10 +4673,10 @@
         <v>2.5</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,13 +3968,13 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>1.6</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>1.55</v>
       </c>
       <c r="W29" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X29" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V30" t="n">
         <v>1.55</v>
       </c>
       <c r="W30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.79166666666</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AO36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45889.52083333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="10">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,46 +2804,46 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="25">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4455,27 +4455,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N30" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>1.55</v>
       </c>
       <c r="W30" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X30" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,31 +4919,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4989,13 +4989,13 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="33">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,31 +5060,31 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="M33" t="n">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5096,23 +5096,23 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
       <c r="AD33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5145,13 +5145,13 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="34">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45889.95833333334</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5433,6 +5433,147 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
+        <v>45889.95833333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,13 +4250,13 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
         <v>1.6</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
         <v>1.6</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,83 +2522,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>3.81</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
         <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="X15" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG15" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,55 +2663,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.33</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
         <v>1.67</v>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2975,16 +2975,16 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
         <v>1.6</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V30" t="n">
         <v>1.55</v>
       </c>
       <c r="W30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X31" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45889.79166666666</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,55 +2522,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.33</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
         <v>1.67</v>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2975,16 +2975,16 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
         <v>1.6</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N30" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>1.55</v>
       </c>
       <c r="W30" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X30" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V31" t="n">
         <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X31" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45889.79166666666</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.25</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,55 +2522,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>1.67</v>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>9.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>1.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3257,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N27" t="n">
-        <v>4.75</v>
+        <v>12.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Z27" t="n">
         <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.73</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.97</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.1</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.25</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M30" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V30" t="n">
         <v>1.55</v>
       </c>
       <c r="W30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X31" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45889.79166666666</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO36"/>
+  <dimension ref="A1:AO37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,12 +930,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45889.45833333334</v>
+        <v>45889.35763888889</v>
       </c>
     </row>
     <row r="5">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1424,16 +1424,16 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45889.52083333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="11">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,55 +2240,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.5</v>
       </c>
-      <c r="P13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X13" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>1.67</v>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>3.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.33</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.5</v>
+        <v>5.1</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X18" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3257,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3398,10 +3398,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="26">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.75</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Z26" t="n">
         <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4596,27 +4596,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,58 +4919,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,31 +5060,31 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5145,13 +5145,13 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="34">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,31 +5201,31 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5237,47 +5237,47 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -5286,13 +5286,13 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="35">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45889.95833333334</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="36">
@@ -5574,6 +5574,147 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
+        <v>45889.95833333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1424,16 +1424,16 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>3.33</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,83 +2945,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.81</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
         <v>1.02</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="X18" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG18" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH18" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>9.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V31" t="n">
         <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X31" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,58 +4919,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>1.55</v>
       </c>
       <c r="W32" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X32" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO37"/>
+  <dimension ref="A1:AO36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1409,43 +1409,43 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45889.52083333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="12">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3257,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,16 +3680,16 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3941,22 +3941,22 @@
         <v>4.33</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3980,10 +3980,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -4002,13 +4002,13 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.65625</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.5</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4364,31 +4364,31 @@
         <v>4.75</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="X28" t="n">
         <v>1.45</v>
@@ -4403,10 +4403,10 @@
         <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,31 +4496,31 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4544,10 +4544,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4566,13 +4566,13 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,19 +4778,19 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" t="n">
         <v>1.53</v>
@@ -4799,7 +4799,7 @@
         <v>2.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
         <v>1.25</v>
@@ -4811,62 +4811,62 @@
         <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X31" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AN31" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4949,16 +4949,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="33">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,31 +5060,31 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5145,13 +5145,13 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="34">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,31 +5201,31 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.67</v>
+        <v>2.84</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="O34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -5271,13 +5271,13 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -5286,13 +5286,13 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.95833333334</v>
       </c>
     </row>
     <row r="36">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5574,147 +5574,6 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
-        <v>45889.95833333334</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Colorado Rapids II</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Portland Timbers II</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,83 +689,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X3" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,95 +2381,95 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O14" t="n">
         <v>3.25</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
         <v>3.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AN14" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.63</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.81</v>
+        <v>3.33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,55 +2945,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.33</v>
       </c>
-      <c r="P18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>1.67</v>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3257,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3368,83 +3368,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.5</v>
+        <v>10.53</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>4.61</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI21" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>4.46</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V22" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3665,43 +3665,43 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W23" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="X23" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3959,13 +3959,13 @@
         <v>1.4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X25" t="n">
         <v>2.05</v>
@@ -3974,10 +3974,10 @@
         <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB25" t="n">
         <v>1.91</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
         <v>2.25</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,95 +4073,95 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P26" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>1.6</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN26" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="X27" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
         <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,92 +4355,92 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O28" t="n">
         <v>1.57</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.53</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="S28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.2</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AI28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.53</v>
       </c>
       <c r="AN28" t="n">
         <v>2.5</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,83 +4496,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.67</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="AB29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.5</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AI29" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.75</v>
+        <v>11</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AI30" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="AN30" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.66666666666</v>
@@ -5210,31 +5210,31 @@
         <v>2.64</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X34" t="n">
         <v>2.25</v>
@@ -5243,16 +5243,16 @@
         <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -5265,19 +5265,19 @@
         </is>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -5286,10 +5286,10 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" s="3" t="n">
         <v>45889.89583333334</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AI3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1409,43 +1409,43 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.89</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>45889.45833333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="8">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.5</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.33</v>
@@ -2537,13 +2537,13 @@
         <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T15" t="n">
         <v>1.5</v>
@@ -2552,22 +2552,22 @@
         <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="X15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.63</v>
+        <v>1.72</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>4.24</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,31 +2945,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3101,43 +3101,43 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45889.58333333334</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.99</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.58333333334</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,83 +3368,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10.53</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.61</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="R21" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="T21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.77</v>
+        <v>5.22</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>2.55</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="N22" t="n">
-        <v>4.46</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,13 +3594,13 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3665,43 +3665,43 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="24">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.64583333334</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.57</v>
       </c>
-      <c r="M26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,19 +4214,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
         <v>1.3</v>
@@ -4235,62 +4235,62 @@
         <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U27" t="n">
         <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,83 +4355,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI28" t="n">
         <v>2.5</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN28" t="n">
         <v>2.5</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M29" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V29" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="X29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,20 +4560,20 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AG29" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AI29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>3</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>11</v>
-      </c>
       <c r="AK29" t="n">
         <v>0</v>
       </c>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AN29" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,83 +4637,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.4</v>
       </c>
-      <c r="R30" t="n">
+      <c r="Y30" t="n">
         <v>2.75</v>
       </c>
-      <c r="S30" t="n">
+      <c r="Z30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI30" t="n">
         <v>3</v>
       </c>
-      <c r="T30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.66666666666</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AI2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>4.24</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>4.24</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.54166666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,55 +3086,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.11</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
         <v>1.57</v>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.42</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z20" t="n">
-        <v>3.77</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>3.08</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.8</v>
+        <v>4.35</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.6</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z21" t="n">
-        <v>5.22</v>
+        <v>3.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.55</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45889.60416666666</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="X26" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="n">
         <v>2.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,95 +4214,95 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.67</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="AB27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.5</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="AI27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.22</v>
       </c>
-      <c r="W27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,92 +4355,92 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O28" t="n">
         <v>1.57</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.53</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="S28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.2</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AI28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.53</v>
       </c>
       <c r="AN28" t="n">
         <v>2.5</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,95 +4496,95 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="O29" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R29" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T29" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="X29" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
         <v>1.6</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN29" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AI30" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="AN30" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45889.66666666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO36"/>
+  <dimension ref="A1:AO33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AI3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>45889.45833333334</v>
+        <v>45889.5</v>
       </c>
     </row>
     <row r="7">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>3.69</v>
       </c>
       <c r="M9" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1776,27 +1776,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45889.5</v>
+        <v>45889.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>51</v>
+        <v>3.36</v>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2678,43 +2678,43 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.75</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45889.54166666666</v>
+        <v>45889.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="W19" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="20">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3242,43 +3242,43 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.625</v>
       </c>
     </row>
     <row r="21">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.5</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
       <c r="P21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.42</v>
-      </c>
       <c r="R21" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="X21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.38</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3435,16 +3435,16 @@
         <v>1.18</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.8</v>
+        <v>4.33</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45889.60416666666</v>
+        <v>45889.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>1.77</v>
       </c>
       <c r="M22" t="n">
-        <v>2.56</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.89</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,13 +3594,13 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.65625</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45889.625</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,83 +3791,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.57</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,13 +3876,13 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45889.64583333334</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O25" t="n">
         <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="X25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AI25" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4020,10 +4020,10 @@
         <v>1.53</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45889.65625</v>
+        <v>45889.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,83 +4355,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W28" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="X28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.5</v>
       </c>
-      <c r="T28" t="n">
+      <c r="AC28" t="n">
         <v>1.5</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AO28" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4455,27 +4455,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,13 +4581,13 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4596,27 +4596,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,59 +4637,59 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4701,34 +4701,34 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
         <v>1.57</v>
       </c>
-      <c r="AH30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AN30" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.66666666666</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="31">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,98 +4778,98 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>2.84</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>2.57</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>2.64</v>
       </c>
       <c r="O31" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="P31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG31" t="n">
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AH31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN31" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.79166666666</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.95833333334</v>
       </c>
     </row>
     <row r="33">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,31 +5060,31 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5145,435 +5145,12 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45889.85416666666</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO34" s="3" t="n">
-        <v>45889.89583333334</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="3" t="n">
-        <v>45889.95833333334</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Colorado Rapids II</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Portland Timbers II</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AI2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.69</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>6.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>5.71</v>
       </c>
       <c r="M10" t="n">
-        <v>51</v>
+        <v>3.92</v>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O10" t="n">
         <v>3.25</v>
@@ -1856,7 +1856,7 @@
         <v>1.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z10" t="n">
         <v>3.2</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,55 +2099,55 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.33</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>1.67</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.77</v>
+        <v>5.22</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>1.38</v>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>2.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.6</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z18" t="n">
-        <v>5.22</v>
+        <v>3.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.55</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,19 +3650,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
         <v>1.3</v>
@@ -3671,37 +3671,37 @@
         <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U23" t="n">
         <v>1.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="X23" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,83 +3791,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.4</v>
       </c>
-      <c r="R24" t="n">
+      <c r="Y24" t="n">
         <v>2.75</v>
       </c>
-      <c r="S24" t="n">
+      <c r="Z24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI24" t="n">
         <v>3</v>
       </c>
-      <c r="T24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,19 +4073,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="O26" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P26" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
         <v>1.3</v>
@@ -4094,62 +4094,62 @@
         <v>3.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U26" t="n">
         <v>1.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.71</v>
+        <v>3.69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>5.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>1.62</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>4.24</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.69</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.79</v>
+        <v>6.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,83 +2663,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>9.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>1.2</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.08</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.35</v>
+        <v>1.8</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2819,16 +2819,16 @@
         <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R17" t="n">
         <v>2.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="U17" t="n">
         <v>1.09</v>
@@ -2852,7 +2852,7 @@
         <v>1.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
         <v>1.57</v>
@@ -2871,16 +2871,16 @@
         <v>1.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5</v>
+        <v>5.57</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.42</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z18" t="n">
-        <v>3.77</v>
+        <v>5.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>3.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.8</v>
+        <v>4.35</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3242,43 +3242,43 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3383,25 +3383,25 @@
         <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="V21" t="n">
         <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="X21" t="n">
         <v>1.62</v>
@@ -3410,16 +3410,16 @@
         <v>2.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
         <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
         <v>2.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="X23" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AG23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH23" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,83 +3791,83 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.22</v>
       </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="R24" t="n">
-        <v>4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W24" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI24" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AN24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.57</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.83</v>
+        <v>4.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.5</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN26" t="n">
         <v>2.5</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="X27" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
         <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>1.61</v>
@@ -1280,31 +1280,31 @@
         <v>1.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.48</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
         <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="n">
         <v>2.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AJ6" t="n">
         <v>5.25</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1746,13 +1746,13 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>3.69</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.24</v>
+        <v>1.79</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.77</v>
+        <v>5.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>3.06</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.8</v>
+        <v>4.35</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>4.61</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="S17" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.22</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>5.57</v>
+        <v>1.83</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.25</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.18</v>
-      </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="X18" t="n">
         <v>2.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.45</v>
+        <v>5.21</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3227,22 +3227,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>2.1</v>
@@ -3254,13 +3254,13 @@
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
         <v>2.97</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AG20" t="n">
         <v>1.45</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,83 +3650,83 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.22</v>
       </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W23" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,19 +3791,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
         <v>1.3</v>
@@ -3812,37 +3812,37 @@
         <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U24" t="n">
         <v>1.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="X24" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="X25" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.57</v>
       </c>
-      <c r="M26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W27" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AG27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH27" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AI27" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AI3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="N9" t="n">
-        <v>4.24</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>4.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.71</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3.92</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
         <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="X13" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>1.78</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>7.75</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>4.61</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.27</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.4</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>1.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>4.61</v>
       </c>
       <c r="N18" t="n">
-        <v>4.25</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.3</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.21</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3012,16 +3012,16 @@
         <v>1.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>1.57</v>
@@ -3386,13 +3386,13 @@
         <v>1.27</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="S21" t="n">
         <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
         <v>1.03</v>
@@ -3404,16 +3404,16 @@
         <v>4.5</v>
       </c>
       <c r="X21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
         <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
         <v>1.57</v>
@@ -3435,10 +3435,10 @@
         <v>1.22</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AI21" t="n">
         <v>2.38</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AG24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.53</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X25" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
         <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>12.2</v>
+        <v>4.75</v>
       </c>
       <c r="O27" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W27" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="X27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Z27" t="n">
         <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,59 +1676,59 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.8</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.43</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.71</v>
+        <v>3.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,55 +2099,55 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.72</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>1.67</v>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>7.75</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2429,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2669,7 +2669,7 @@
         <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2693,10 +2693,10 @@
         <v>1.13</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="X16" t="n">
         <v>2.66</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.25</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.21</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2871,16 +2871,16 @@
         <v>1.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>4.61</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.27</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.4</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="X18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3012,16 +3012,16 @@
         <v>1.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
         <v>2.05</v>
@@ -3260,7 +3260,7 @@
         <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
         <v>2.97</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,95 +3932,95 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>1.6</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN25" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.53</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X27" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
         <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AI2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.71</v>
+        <v>3.69</v>
       </c>
       <c r="M9" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2000,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,83 +2099,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
         <v>1.22</v>
       </c>
-      <c r="W12" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,95 +2381,95 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.72</v>
+        <v>5.71</v>
       </c>
       <c r="M14" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
         <v>3.3</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="X14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
         <v>3.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AN14" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.25</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="U16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="X16" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.35</v>
+        <v>5.21</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.7</v>
+        <v>5.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>3.06</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.83</v>
+        <v>4.35</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.21</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3012,16 +3012,16 @@
         <v>1.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>1.57</v>
@@ -3383,7 +3383,7 @@
         <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R21" t="n">
         <v>3.4</v>
@@ -3398,22 +3398,22 @@
         <v>1.03</v>
       </c>
       <c r="V21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
         <v>4.5</v>
       </c>
       <c r="X21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z21" t="n">
         <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
         <v>1.57</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AG21" t="n">
         <v>1.95</v>
@@ -3444,7 +3444,7 @@
         <v>2.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.57</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="X26" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="n">
         <v>2.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,95 +4214,95 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.53</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,19 +4355,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
         <v>1.53</v>
@@ -4376,7 +4376,7 @@
         <v>2.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
         <v>1.25</v>
@@ -4385,28 +4385,28 @@
         <v>1.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="X28" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AN28" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,13 +4581,13 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO29" s="3" t="n">
-        <v>45889.83333333334</v>
+        <v>45889.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4707,13 +4707,13 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
-        <v>45889.85416666666</v>
+        <v>45889.83333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,98 +4778,98 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.57</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="AH31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN31" t="n">
         <v>2.5</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AO31" s="3" t="n">
-        <v>45889.89583333334</v>
+        <v>45889.85416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,58 +4919,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45889.95833333334</v>
+        <v>45889.89583333334</v>
       </c>
     </row>
     <row r="33">
@@ -5024,133 +5024,274 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>45889.95833333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Colorado Rapids II</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Portland Timbers II</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="3" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3" t="n">
         <v>45889.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AI3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.69</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>4.24</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1994,22 +1994,22 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,95 +2240,95 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>5.71</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>3.92</v>
       </c>
       <c r="N13" t="n">
-        <v>6.5</v>
+        <v>1.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="U13" t="n">
         <v>1.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AN13" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.71</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.92</v>
+        <v>6.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.64</v>
+        <v>15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>3.69</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>4.24</v>
+        <v>1.79</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.21</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2730,16 +2730,16 @@
         <v>1.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="R18" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="X18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>5.21</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3012,16 +3012,16 @@
         <v>1.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="AN24" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>12.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.4</v>
       </c>
-      <c r="R25" t="n">
+      <c r="Y25" t="n">
         <v>2.75</v>
       </c>
-      <c r="S25" t="n">
+      <c r="Z25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI25" t="n">
         <v>3</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,19 +4355,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.53</v>
@@ -4376,7 +4376,7 @@
         <v>2.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
         <v>1.25</v>
@@ -4385,65 +4385,65 @@
         <v>1.1</v>
       </c>
       <c r="V28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.5</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,19 +4496,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
         <v>1.53</v>
@@ -4517,7 +4517,7 @@
         <v>2.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
         <v>1.25</v>
@@ -4526,28 +4526,28 @@
         <v>1.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="X29" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AN29" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>3.69</v>
       </c>
       <c r="M9" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="AF9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.77</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,31 +1958,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N11" t="n">
-        <v>4.24</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.71</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.64</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="X13" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Z13" t="n">
         <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>5.16</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.15</v>
       </c>
-      <c r="M14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>15</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,95 +2663,95 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.5</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.7</v>
+        <v>5.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>3.07</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AJ16" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.83</v>
       </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AN16" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
         <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
         <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.25</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,84 +2945,84 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W18" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.37</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.21</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI18" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AJ18" t="n">
         <v>1.75</v>
       </c>
-      <c r="AH18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3242,19 +3242,19 @@
         <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
         <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
         <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="V20" t="n">
         <v>1.65</v>
@@ -3263,7 +3263,7 @@
         <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AG20" t="n">
         <v>1.45</v>
@@ -3392,16 +3392,16 @@
         <v>2.32</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
         <v>1.03</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="X21" t="n">
         <v>1.62</v>
@@ -3438,13 +3438,13 @@
         <v>1.95</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>4.19</v>
+        <v>3.61</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,83 +3650,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.45</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.83</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P23" t="n">
         <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W23" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.5</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN23" t="n">
         <v>2.5</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="R24" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U24" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="X24" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
         <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.22</v>
       </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W25" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="X25" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI25" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AN25" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
         <v>3.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P26" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="n">
         <v>2.88</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>12.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="R27" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="U27" t="n">
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W27" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="X27" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4511,19 +4511,19 @@
         <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R29" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="V29" t="n">
         <v>1.5</v>
@@ -4538,16 +4538,16 @@
         <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="U10" t="n">
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>5.35</v>
+        <v>3.28</v>
       </c>
       <c r="X10" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,31 +1881,31 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.75</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI10" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN10" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>5.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.71</v>
+        <v>1.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="N14" t="n">
-        <v>1.64</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>4.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>10.7</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.84</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="X17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.6</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z17" t="n">
-        <v>5.21</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,20 +2868,20 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AG17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.75</v>
       </c>
-      <c r="AH17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>5</v>
-      </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,95 +2945,95 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.5</v>
+        <v>1.84</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="T18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="V18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.4</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN18" t="n">
         <v>2.9</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AG24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,19 +3932,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
         <v>1.3</v>
@@ -3953,37 +3953,37 @@
         <v>3.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U25" t="n">
         <v>1.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="X25" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,83 +4214,83 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.22</v>
       </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P27" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W27" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="X27" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH27" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>4.75</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,95 +4355,95 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.53</v>
       </c>
-      <c r="P28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="Z28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>2.38</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN28" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,95 +4496,95 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R29" t="n">
         <v>2.38</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W29" t="n">
         <v>2.5</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.5</v>
       </c>
-      <c r="W29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AN29" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.69</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.71</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="X11" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>4.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>10.7</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,83 +2099,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.15</v>
       </c>
-      <c r="M12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.2</v>
+        <v>3.69</v>
       </c>
       <c r="M14" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>1.79</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.75</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,19 +2663,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
         <v>1.6</v>
@@ -2684,37 +2684,37 @@
         <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T16" t="n">
         <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.25</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.61</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2828,7 +2828,7 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="U17" t="n">
         <v>1.03</v>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AH17" t="n">
         <v>9</v>
@@ -2880,7 +2880,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
         <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S18" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="U18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.21</v>
+        <v>5.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5</v>
+        <v>4.61</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3386,7 +3386,7 @@
         <v>1.25</v>
       </c>
       <c r="R21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S21" t="n">
         <v>2.32</v>
@@ -3401,7 +3401,7 @@
         <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="X21" t="n">
         <v>1.62</v>
@@ -3413,7 +3413,7 @@
         <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
         <v>1.57</v>
@@ -3438,7 +3438,7 @@
         <v>1.95</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AI21" t="n">
         <v>2.3</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,83 +3650,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.25</v>
       </c>
-      <c r="R23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AB23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3968,10 +3968,10 @@
         <v>4.33</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z25" t="n">
         <v>2.35</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="O26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.83</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.68</v>
-      </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,31 +4137,31 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AG26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.57</v>
       </c>
-      <c r="AH26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AN26" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,83 +4214,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.45</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.83</v>
-      </c>
       <c r="O27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.5</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN27" t="n">
         <v>2.5</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,95 +4355,95 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R28" t="n">
         <v>2.38</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W28" t="n">
         <v>2.5</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.5</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,95 +4496,95 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
         <v>2.38</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN29" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="T9" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.75</v>
+        <v>3.93</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,52 +1823,52 @@
         <v>6.8</v>
       </c>
       <c r="N10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>6.2</v>
+        <v>3.97</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>1.62</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.75</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10.7</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,52 +2240,52 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.85</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2396,43 +2396,43 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="U16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="W16" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.21</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,95 +2804,95 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="R17" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="V17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.4</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN17" t="n">
         <v>2.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,59 +2945,59 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>9.4</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="R18" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="X18" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z18" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.07</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.61</v>
+        <v>1.82</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.57</v>
@@ -3389,7 +3389,7 @@
         <v>3.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
         <v>1.53</v>
@@ -3401,13 +3401,13 @@
         <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="X21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
         <v>2.4</v>
@@ -3416,7 +3416,7 @@
         <v>1.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
         <v>2.25</v>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AG21" t="n">
         <v>1.95</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AI21" t="n">
         <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,19 +3932,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
         <v>1.3</v>
@@ -3953,62 +3953,62 @@
         <v>3.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U25" t="n">
         <v>1.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="X25" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI25" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N26" t="n">
         <v>3.45</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.83</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.5</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN26" t="n">
         <v>2.5</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.53</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X27" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="N29" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="O29" t="n">
         <v>2.38</v>
@@ -4511,7 +4511,7 @@
         <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R29" t="n">
         <v>2.5</v>
@@ -4520,22 +4520,22 @@
         <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="U29" t="n">
         <v>1.06</v>
       </c>
       <c r="V29" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="X29" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="Z29" t="n">
         <v>4</v>
@@ -4563,16 +4563,16 @@
         <v>1.36</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.05</v>
+        <v>5.35</v>
       </c>
       <c r="X9" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.76</v>
+        <v>4.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.93</v>
+        <v>10.7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="M10" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>5.35</v>
+        <v>4.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.66</v>
+        <v>2.23</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.93</v>
+        <v>2.26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10.7</v>
+        <v>3.93</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.97</v>
+        <v>6.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.62</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,83 +2240,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.15</v>
       </c>
-      <c r="M13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>15</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2396,43 +2396,43 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="T15" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="U15" t="n">
         <v>1.03</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.25</v>
+        <v>3.74</v>
       </c>
       <c r="AI15" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="U16" t="n">
         <v>1.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.25</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.35</v>
+        <v>5.58</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>9.4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.33</v>
-      </c>
       <c r="X17" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.21</v>
+        <v>3.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5.58</v>
+        <v>1.82</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.4</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.82</v>
+        <v>4.35</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.45</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.83</v>
-      </c>
       <c r="O25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
         <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI25" t="n">
         <v>2.5</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AN25" t="n">
         <v>2.5</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,92 +4073,92 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.83</v>
       </c>
       <c r="O26" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.2</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AI26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.53</v>
       </c>
       <c r="AN26" t="n">
         <v>2.5</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AI2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1682,52 +1682,52 @@
         <v>6.8</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>4.05</v>
+        <v>5.35</v>
       </c>
       <c r="X10" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>4.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.93</v>
+        <v>10.7</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="U12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="X12" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.9</v>
+        <v>3.93</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W15" t="n">
         <v>3.3</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.94</v>
-      </c>
       <c r="X15" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.74</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="U16" t="n">
         <v>1.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="W16" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="X16" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.21</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AJ16" t="n">
-        <v>5.58</v>
+        <v>4.35</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,95 +2804,95 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.4</v>
+        <v>1.88</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="R17" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>1.33</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="AG17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN17" t="n">
         <v>2.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,59 +2945,59 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="R18" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="X18" t="n">
-        <v>2.69</v>
+        <v>2.14</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.35</v>
+        <v>1.82</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y23" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="n">
         <v>2.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="AN24" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,92 +3932,92 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P25" t="n">
         <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R25" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.2</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AI25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.53</v>
       </c>
       <c r="AN25" t="n">
         <v>2.5</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,95 +4073,95 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.83</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.5</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="AI26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.22</v>
       </c>
-      <c r="W26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AN26" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,95 +4214,95 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.53</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AN27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4499,7 +4499,7 @@
         <v>3.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
         <v>2.39</v>
@@ -4511,13 +4511,13 @@
         <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
         <v>2.5</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>1.3</v>
@@ -4529,25 +4529,25 @@
         <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="X29" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Y29" t="n">
         <v>1.62</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA29" t="n">
         <v>1.16</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>1.36</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="AI29" t="n">
         <v>2.12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AI3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>5.35</v>
+        <v>3.94</v>
       </c>
       <c r="X10" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.75</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>3.74</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10.7</v>
+        <v>2.55</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="R12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
         <v>3.3</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4.05</v>
-      </c>
       <c r="X12" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.93</v>
+        <v>4.9</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>3.94</v>
+        <v>5.35</v>
       </c>
       <c r="X14" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="Y14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.07</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AC14" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>4.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.74</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.55</v>
+        <v>10.7</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,59 +2663,59 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="R16" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="V16" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="X16" t="n">
-        <v>2.69</v>
+        <v>2.14</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.35</v>
+        <v>1.82</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.4</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.82</v>
+        <v>4.35</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,19 +3650,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
         <v>1.3</v>
@@ -3671,62 +3671,62 @@
         <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
         <v>1.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="X24" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,95 +3932,95 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.57</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AH25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.53</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X27" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.05</v>
+        <v>5.35</v>
       </c>
       <c r="X9" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.76</v>
+        <v>4.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.26</v>
+        <v>2.93</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.93</v>
+        <v>10.7</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,22 +1781,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.25</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.38</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W10" t="n">
         <v>3.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.94</v>
-      </c>
       <c r="X10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.74</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,83 +2099,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.67</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="AC12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
         <v>1.29</v>
       </c>
-      <c r="W12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2387,52 +2387,52 @@
         <v>6.8</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
         <v>4.75</v>
@@ -2678,10 +2678,10 @@
         <v>1.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2696,22 +2696,22 @@
         <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="X16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
         <v>1.44</v>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.18</v>
+        <v>3.1</v>
       </c>
       <c r="AG16" t="n">
         <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,83 +2804,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH17" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AI17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5.58</v>
+        <v>4.2</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,84 +2945,84 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
         <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>5.5</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>4.35</v>
-      </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>1.57</v>
@@ -3383,43 +3383,43 @@
         <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="S21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
         <v>1.03</v>
       </c>
       <c r="V21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.57</v>
       </c>
-      <c r="Y21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.69</v>
+        <v>3.8</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,95 +3650,95 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>12.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.5</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="AI23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
         <v>1.22</v>
       </c>
-      <c r="W23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AN23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.53</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X24" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>12.2</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="X26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,19 +4214,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
         <v>1.3</v>
@@ -4235,62 +4235,62 @@
         <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U27" t="n">
         <v>1.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="X27" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,95 +4355,95 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.62</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="Z28" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>2.38</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN28" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,83 +4496,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P29" t="n">
         <v>3.2</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R29" t="n">
         <v>2.38</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.5</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI29" t="n">
         <v>2</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>3.11</v>
+        <v>6.5</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1013,10 +1013,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45889.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45889.5</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,58 +1817,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.97</v>
+        <v>6.8</v>
       </c>
       <c r="N10" t="n">
-        <v>1.62</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,83 +1958,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P11" t="n">
         <v>3.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI11" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,83 +2099,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>5.71</v>
       </c>
       <c r="M12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
         <v>3.25</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.9</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
         <v>1.25</v>
       </c>
-      <c r="W12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.02</v>
+        <v>5.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,83 +2240,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
         <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="S13" t="n">
-        <v>2.41</v>
+        <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="U13" t="n">
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
         <v>1.2</v>
       </c>
-      <c r="W13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>3.69</v>
       </c>
       <c r="M14" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>15</v>
+        <v>1.79</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,83 +2663,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="X16" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>4.75</v>
+        <v>1.83</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.12</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.6</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z17" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,20 +2868,20 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.7</v>
@@ -2975,16 +2975,16 @@
         <v>1.09</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="X18" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
         <v>5.25</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45889.625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45889.625</v>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>1.57</v>
@@ -3404,10 +3404,10 @@
         <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z21" t="n">
         <v>2.52</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>12.2</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="U23" t="n">
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="X23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AG23" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O24" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="n">
         <v>2.88</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y25" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Z25" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="n">
         <v>2.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>12.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="R26" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W26" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="X26" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,83 +4355,83 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P28" t="n">
         <v>3.2</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R28" t="n">
         <v>2.38</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.5</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI28" t="n">
         <v>2</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>3.11</v>
+        <v>6.5</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,95 +4496,95 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
         <v>2.38</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN29" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -689,95 +689,95 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AI2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.25</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45889.29166666666</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -830,95 +830,95 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.85</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>45889.29166666666</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,83 +1817,83 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.15</v>
       </c>
-      <c r="M10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>45889.54166666666</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>3.69</v>
       </c>
       <c r="M11" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>1.79</v>
       </c>
       <c r="O11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.33</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="U11" t="n">
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="X11" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.51</v>
+        <v>4.02</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>2.55</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.71</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="T12" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="X12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Y12" t="n">
         <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.25</v>
+        <v>2.54</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P13" t="n">
         <v>3.7</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="R13" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="X13" t="n">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.02</v>
+        <v>4.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.85</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.68</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45889.54166666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>2.95</v>
+        <v>2.37</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.85</v>
+        <v>5.5</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,84 +2945,84 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.85</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.53</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X23" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="X24" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O25" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH25" t="n">
         <v>2.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45889.66666666666</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,95 +4355,95 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>3.11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>2.38</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN28" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45889.79166666666</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,95 +4496,95 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.11</v>
+        <v>1.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.14</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R29" t="n">
         <v>2.38</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W29" t="n">
         <v>2.5</v>
       </c>
-      <c r="S29" t="n">
+      <c r="X29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN29" t="n">
         <v>3.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.83</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45889.79166666666</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>

--- a/jogos_2025-08-20.xlsx
+++ b/jogos_2025-08-20.xlsx
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,95 +2663,95 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="T16" t="n">
         <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="X16" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AH16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN16" t="n">
         <v>2.9</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.5</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45889.60416666666</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="T17" t="n">
         <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="X17" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,31 +2868,31 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN17" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.9</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45889.60416666666</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.5</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
         <v>2.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45889.66666666666</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.53</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="X24" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.18</v>
+    